--- a/data/T1_raw.xlsx
+++ b/data/T1_raw.xlsx
@@ -2550,7 +2550,7 @@
         <v>2</v>
       </c>
       <c r="AX2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY2">
         <v>4</v>
@@ -2750,7 +2750,7 @@
         <v>3</v>
       </c>
       <c r="AX3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY3">
         <v>2</v>
@@ -3350,7 +3350,7 @@
         <v>3</v>
       </c>
       <c r="AX6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY6">
         <v>4</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="AX7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY7">
         <v>1</v>
@@ -3950,7 +3950,7 @@
         <v>1</v>
       </c>
       <c r="AX9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY9">
         <v>3</v>
@@ -5150,7 +5150,7 @@
         <v>0</v>
       </c>
       <c r="AX15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY15">
         <v>3</v>
@@ -6150,7 +6150,7 @@
         <v>6</v>
       </c>
       <c r="AX20">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY20">
         <v>3</v>
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="AX26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY26">
         <v>2</v>
@@ -7550,7 +7550,7 @@
         <v>0</v>
       </c>
       <c r="AX27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY27">
         <v>3</v>
@@ -8350,7 +8350,7 @@
         <v>6</v>
       </c>
       <c r="AX31">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AY31">
         <v>3</v>
@@ -8747,7 +8747,7 @@
         <v>4</v>
       </c>
       <c r="AX33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY33">
         <v>4</v>
@@ -8947,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="AX34">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY34">
         <v>4</v>
@@ -11544,7 +11544,7 @@
         <v>2</v>
       </c>
       <c r="AX47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY47">
         <v>4</v>
@@ -15344,7 +15344,7 @@
         <v>4</v>
       </c>
       <c r="AX66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY66">
         <v>5</v>
@@ -15544,7 +15544,7 @@
         <v>1</v>
       </c>
       <c r="AX67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY67">
         <v>3</v>
@@ -15744,7 +15744,7 @@
         <v>4</v>
       </c>
       <c r="AX68">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY68">
         <v>4</v>
@@ -16744,7 +16744,7 @@
         <v>3</v>
       </c>
       <c r="AX73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY73">
         <v>1</v>
@@ -16944,7 +16944,7 @@
         <v>0</v>
       </c>
       <c r="AX74">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY74">
         <v>4</v>
@@ -18144,7 +18144,7 @@
         <v>0</v>
       </c>
       <c r="AX80">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY80">
         <v>4</v>
@@ -18744,7 +18744,7 @@
         <v>4</v>
       </c>
       <c r="AX83">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY83">
         <v>1</v>
@@ -19941,7 +19941,7 @@
         <v>0</v>
       </c>
       <c r="AX89">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY89">
         <v>2</v>
@@ -20341,7 +20341,7 @@
         <v>0</v>
       </c>
       <c r="AX91">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY91">
         <v>3</v>
@@ -22141,7 +22141,7 @@
         <v>2</v>
       </c>
       <c r="AX100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY100">
         <v>2</v>
@@ -22341,7 +22341,7 @@
         <v>6</v>
       </c>
       <c r="AX101">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY101">
         <v>3</v>
@@ -25341,7 +25341,7 @@
         <v>3</v>
       </c>
       <c r="AX116">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY116">
         <v>3</v>
@@ -27141,7 +27141,7 @@
         <v>9</v>
       </c>
       <c r="AX125">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY125">
         <v>3</v>
@@ -29941,7 +29941,7 @@
         <v>0</v>
       </c>
       <c r="AX139">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY139">
         <v>3</v>
@@ -30541,7 +30541,7 @@
         <v>3</v>
       </c>
       <c r="AX142">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY142">
         <v>4</v>
@@ -31541,7 +31541,7 @@
         <v>4</v>
       </c>
       <c r="AX147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY147">
         <v>2</v>
@@ -31741,7 +31741,7 @@
         <v>2</v>
       </c>
       <c r="AX148">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AY148">
         <v>3</v>
@@ -31941,7 +31941,7 @@
         <v>3</v>
       </c>
       <c r="AX149">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY149">
         <v>4</v>
@@ -32938,7 +32938,7 @@
         <v>3</v>
       </c>
       <c r="AX154">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY154">
         <v>3</v>
@@ -33138,7 +33138,7 @@
         <v>3</v>
       </c>
       <c r="AX155">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY155">
         <v>4</v>
@@ -33538,7 +33538,7 @@
         <v>3</v>
       </c>
       <c r="AX157">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY157">
         <v>4</v>
@@ -34138,7 +34138,7 @@
         <v>1</v>
       </c>
       <c r="AX160">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AY160">
         <v>3</v>
@@ -36938,7 +36938,7 @@
         <v>2</v>
       </c>
       <c r="AX174">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY174">
         <v>5</v>
@@ -37138,7 +37138,7 @@
         <v>6</v>
       </c>
       <c r="AX175">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY175">
         <v>4</v>
@@ -37938,7 +37938,7 @@
         <v>2</v>
       </c>
       <c r="AX179">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY179">
         <v>2</v>
@@ -40138,7 +40138,7 @@
         <v>1</v>
       </c>
       <c r="AX190">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AY190">
         <v>3</v>
@@ -46135,7 +46135,7 @@
         <v>2</v>
       </c>
       <c r="AX220">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY220">
         <v>3</v>
@@ -46335,7 +46335,7 @@
         <v>0</v>
       </c>
       <c r="AX221">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY221">
         <v>1</v>
@@ -46735,7 +46735,7 @@
         <v>2</v>
       </c>
       <c r="AX223">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY223">
         <v>3</v>
@@ -46935,7 +46935,7 @@
         <v>1</v>
       </c>
       <c r="AX224">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY224">
         <v>3</v>
@@ -48735,7 +48735,7 @@
         <v>4</v>
       </c>
       <c r="AX233">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="AY233">
         <v>4</v>
@@ -48935,7 +48935,7 @@
         <v>4</v>
       </c>
       <c r="AX234">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY234">
         <v>2</v>
@@ -49535,7 +49535,7 @@
         <v>4</v>
       </c>
       <c r="AX237">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY237">
         <v>4</v>
@@ -49735,7 +49735,7 @@
         <v>1</v>
       </c>
       <c r="AX238">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AY238">
         <v>3</v>
@@ -50335,7 +50335,7 @@
         <v>5</v>
       </c>
       <c r="AX241">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY241">
         <v>2</v>
@@ -51535,7 +51535,7 @@
         <v>0</v>
       </c>
       <c r="AX247">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY247">
         <v>4</v>
@@ -53135,7 +53135,7 @@
         <v>0</v>
       </c>
       <c r="AX255">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY255">
         <v>4</v>
@@ -55132,7 +55132,7 @@
         <v>5</v>
       </c>
       <c r="AX265">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY265">
         <v>2</v>
@@ -56332,7 +56332,7 @@
         <v>4</v>
       </c>
       <c r="AX271">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY271">
         <v>2</v>
@@ -57732,7 +57732,7 @@
         <v>0</v>
       </c>
       <c r="AX278">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY278">
         <v>2</v>
@@ -58529,7 +58529,7 @@
         <v>1</v>
       </c>
       <c r="AX282">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="AY282">
         <v>3</v>
@@ -60129,7 +60129,7 @@
         <v>1</v>
       </c>
       <c r="AX290">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY290">
         <v>4</v>
@@ -60929,7 +60929,7 @@
         <v>0</v>
       </c>
       <c r="AX294">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY294">
         <v>4</v>
@@ -61329,7 +61329,7 @@
         <v>6</v>
       </c>
       <c r="AX296">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AY296">
         <v>4</v>
@@ -62129,7 +62129,7 @@
         <v>3</v>
       </c>
       <c r="AX300">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AY300">
         <v>5</v>
@@ -63529,7 +63529,7 @@
         <v>3</v>
       </c>
       <c r="AX307">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY307">
         <v>4</v>
@@ -64329,7 +64329,7 @@
         <v>5</v>
       </c>
       <c r="AX311">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY311">
         <v>3</v>
@@ -64929,7 +64929,7 @@
         <v>2</v>
       </c>
       <c r="AX314">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY314">
         <v>5</v>
@@ -65129,7 +65129,7 @@
         <v>5</v>
       </c>
       <c r="AX315">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY315">
         <v>4</v>
@@ -65729,7 +65729,7 @@
         <v>6</v>
       </c>
       <c r="AX318">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY318">
         <v>3</v>
@@ -68329,7 +68329,7 @@
         <v>1</v>
       </c>
       <c r="AX331">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="AY331">
         <v>1</v>
@@ -69129,7 +69129,7 @@
         <v>6</v>
       </c>
       <c r="AX335">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY335">
         <v>3</v>
@@ -69329,7 +69329,7 @@
         <v>4</v>
       </c>
       <c r="AX336">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY336">
         <v>3</v>
@@ -70929,7 +70929,7 @@
         <v>1</v>
       </c>
       <c r="AX344">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY344">
         <v>4</v>
@@ -71329,7 +71329,7 @@
         <v>5</v>
       </c>
       <c r="AX346">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY346">
         <v>2</v>
@@ -72129,7 +72129,7 @@
         <v>0</v>
       </c>
       <c r="AX350">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AY350">
         <v>3</v>
@@ -74529,7 +74529,7 @@
         <v>3</v>
       </c>
       <c r="AX362">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY362">
         <v>3</v>
@@ -74929,7 +74929,7 @@
         <v>1</v>
       </c>
       <c r="AX364">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY364">
         <v>3</v>
@@ -77729,7 +77729,7 @@
         <v>5</v>
       </c>
       <c r="AX378">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY378">
         <v>2</v>
@@ -80329,7 +80329,7 @@
         <v>1</v>
       </c>
       <c r="AX391">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY391">
         <v>4</v>
@@ -80726,7 +80726,7 @@
         <v>0</v>
       </c>
       <c r="AX393">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AY393">
         <v>4</v>
@@ -80926,7 +80926,7 @@
         <v>7</v>
       </c>
       <c r="AX394">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY394">
         <v>2</v>
@@ -82723,7 +82723,7 @@
         <v>7</v>
       </c>
       <c r="AX403">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY403">
         <v>3</v>
@@ -83123,7 +83123,7 @@
         <v>3</v>
       </c>
       <c r="AX405">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY405">
         <v>4</v>
@@ -86923,7 +86923,7 @@
         <v>5</v>
       </c>
       <c r="AX424">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY424">
         <v>5</v>
@@ -87123,7 +87123,7 @@
         <v>8</v>
       </c>
       <c r="AX425">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY425">
         <v>1</v>
@@ -87923,7 +87923,7 @@
         <v>0</v>
       </c>
       <c r="AX429">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY429">
         <v>4</v>
@@ -88920,7 +88920,7 @@
         <v>5</v>
       </c>
       <c r="AX434">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY434">
         <v>2</v>
@@ -89120,7 +89120,7 @@
         <v>5</v>
       </c>
       <c r="AX435">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY435">
         <v>4</v>
@@ -89720,7 +89720,7 @@
         <v>5</v>
       </c>
       <c r="AX438">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY438">
         <v>3</v>
@@ -91520,7 +91520,7 @@
         <v>0</v>
       </c>
       <c r="AX447">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AY447">
         <v>5</v>
@@ -92120,7 +92120,7 @@
         <v>2</v>
       </c>
       <c r="AX450">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY450">
         <v>4</v>
@@ -93720,7 +93720,7 @@
         <v>2</v>
       </c>
       <c r="AX458">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AY458">
         <v>2</v>
@@ -94120,7 +94120,7 @@
         <v>8</v>
       </c>
       <c r="AX460">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY460">
         <v>3</v>

--- a/data/T1_raw.xlsx
+++ b/data/T1_raw.xlsx
@@ -2544,7 +2544,7 @@
         <v>3</v>
       </c>
       <c r="AV2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2">
         <v>2</v>
@@ -3344,7 +3344,7 @@
         <v>2</v>
       </c>
       <c r="AV6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW6">
         <v>3</v>
@@ -4744,7 +4744,7 @@
         <v>4</v>
       </c>
       <c r="AV13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW13">
         <v>19</v>
@@ -5144,7 +5144,7 @@
         <v>3</v>
       </c>
       <c r="AV15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW15">
         <v>1</v>
@@ -6144,7 +6144,7 @@
         <v>4</v>
       </c>
       <c r="AV20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW20">
         <v>6</v>
@@ -7144,7 +7144,7 @@
         <v>3</v>
       </c>
       <c r="AV25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW25">
         <v>10</v>
@@ -8344,7 +8344,7 @@
         <v>2</v>
       </c>
       <c r="AV31">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW31">
         <v>6</v>
@@ -8743,6 +8743,9 @@
       <c r="AU33">
         <v>3</v>
       </c>
+      <c r="AV33">
+        <v>2</v>
+      </c>
       <c r="AW33">
         <v>4</v>
       </c>
@@ -9141,7 +9144,7 @@
         <v>3</v>
       </c>
       <c r="AV35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW35">
         <v>4</v>
@@ -10738,7 +10741,7 @@
         <v>2</v>
       </c>
       <c r="AV43">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW43">
         <v>8</v>
@@ -13338,7 +13341,7 @@
         <v>3</v>
       </c>
       <c r="AV56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW56">
         <v>19</v>
@@ -13538,7 +13541,7 @@
         <v>5</v>
       </c>
       <c r="AV57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW57">
         <v>17</v>
@@ -13938,7 +13941,7 @@
         <v>3</v>
       </c>
       <c r="AV59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW59">
         <v>9</v>
@@ -14938,7 +14941,7 @@
         <v>4</v>
       </c>
       <c r="AV64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW64">
         <v>15</v>
@@ -16538,7 +16541,7 @@
         <v>3</v>
       </c>
       <c r="AV72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW72">
         <v>7</v>
@@ -16738,7 +16741,7 @@
         <v>4</v>
       </c>
       <c r="AV73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW73">
         <v>3</v>
@@ -17138,7 +17141,7 @@
         <v>4</v>
       </c>
       <c r="AV75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW75">
         <v>12</v>
@@ -17338,7 +17341,7 @@
         <v>3</v>
       </c>
       <c r="AV76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW76">
         <v>8</v>
@@ -17538,7 +17541,7 @@
         <v>3</v>
       </c>
       <c r="AV77">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW77">
         <v>13</v>
@@ -19535,7 +19538,7 @@
         <v>3</v>
       </c>
       <c r="AV87">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW87">
         <v>6</v>
@@ -19935,7 +19938,7 @@
         <v>3</v>
       </c>
       <c r="AV89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW89">
         <v>1</v>
@@ -20535,7 +20538,7 @@
         <v>4</v>
       </c>
       <c r="AV92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW92">
         <v>11</v>
@@ -20735,7 +20738,7 @@
         <v>3</v>
       </c>
       <c r="AV93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW93">
         <v>3</v>
@@ -21135,7 +21138,7 @@
         <v>3</v>
       </c>
       <c r="AV95">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW95">
         <v>12</v>
@@ -22335,7 +22338,7 @@
         <v>4</v>
       </c>
       <c r="AV101">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW101">
         <v>6</v>
@@ -23335,7 +23338,7 @@
         <v>4</v>
       </c>
       <c r="AV106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW106">
         <v>7</v>
@@ -23535,7 +23538,7 @@
         <v>3</v>
       </c>
       <c r="AV107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW107">
         <v>9</v>
@@ -24135,7 +24138,7 @@
         <v>2</v>
       </c>
       <c r="AV110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW110">
         <v>13</v>
@@ -24535,7 +24538,7 @@
         <v>4</v>
       </c>
       <c r="AV112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW112">
         <v>8</v>
@@ -25135,7 +25138,7 @@
         <v>4</v>
       </c>
       <c r="AV115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW115">
         <v>10</v>
@@ -26735,7 +26738,7 @@
         <v>2</v>
       </c>
       <c r="AV123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW123">
         <v>9</v>
@@ -27535,7 +27538,7 @@
         <v>3</v>
       </c>
       <c r="AV127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW127">
         <v>9</v>
@@ -28535,7 +28538,7 @@
         <v>2</v>
       </c>
       <c r="AV132">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW132">
         <v>12</v>
@@ -29535,7 +29538,7 @@
         <v>3</v>
       </c>
       <c r="AV137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW137">
         <v>14</v>
@@ -29935,7 +29938,7 @@
         <v>5</v>
       </c>
       <c r="AV139">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW139">
         <v>1</v>
@@ -30335,7 +30338,7 @@
         <v>2</v>
       </c>
       <c r="AV141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW141">
         <v>7</v>
@@ -31335,7 +31338,7 @@
         <v>3</v>
       </c>
       <c r="AV146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW146">
         <v>9</v>
@@ -31535,7 +31538,7 @@
         <v>3</v>
       </c>
       <c r="AV147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW147">
         <v>4</v>
@@ -32135,7 +32138,7 @@
         <v>3</v>
       </c>
       <c r="AV150">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW150">
         <v>16</v>
@@ -33532,7 +33535,7 @@
         <v>4</v>
       </c>
       <c r="AV157">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW157">
         <v>3</v>
@@ -33932,7 +33935,7 @@
         <v>3</v>
       </c>
       <c r="AV159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW159">
         <v>16</v>
@@ -34132,7 +34135,7 @@
         <v>2</v>
       </c>
       <c r="AV160">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW160">
         <v>1</v>
@@ -34732,7 +34735,7 @@
         <v>3</v>
       </c>
       <c r="AV163">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW163">
         <v>5</v>
@@ -35732,7 +35735,7 @@
         <v>3</v>
       </c>
       <c r="AV168">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW168">
         <v>19</v>
@@ -35932,7 +35935,7 @@
         <v>5</v>
       </c>
       <c r="AV169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW169">
         <v>17</v>
@@ -36132,7 +36135,7 @@
         <v>2</v>
       </c>
       <c r="AV170">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW170">
         <v>13</v>
@@ -38332,7 +38335,7 @@
         <v>5</v>
       </c>
       <c r="AV181">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW181">
         <v>18</v>
@@ -38932,7 +38935,7 @@
         <v>4</v>
       </c>
       <c r="AV184">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW184">
         <v>12</v>
@@ -40132,7 +40135,7 @@
         <v>4</v>
       </c>
       <c r="AV190">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW190">
         <v>1</v>
@@ -40932,7 +40935,7 @@
         <v>4</v>
       </c>
       <c r="AV194">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW194">
         <v>6</v>
@@ -42532,7 +42535,7 @@
         <v>4</v>
       </c>
       <c r="AV202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW202">
         <v>10</v>
@@ -43529,7 +43532,7 @@
         <v>3</v>
       </c>
       <c r="AV207">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW207">
         <v>10</v>
@@ -43729,7 +43732,7 @@
         <v>2</v>
       </c>
       <c r="AV208">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW208">
         <v>6</v>
@@ -45529,7 +45532,7 @@
         <v>3</v>
       </c>
       <c r="AV217">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW217">
         <v>14</v>
@@ -46729,7 +46732,7 @@
         <v>3</v>
       </c>
       <c r="AV223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW223">
         <v>2</v>
@@ -46929,7 +46932,7 @@
         <v>3</v>
       </c>
       <c r="AV224">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW224">
         <v>1</v>
@@ -47729,7 +47732,7 @@
         <v>2</v>
       </c>
       <c r="AV228">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW228">
         <v>22</v>
@@ -47929,7 +47932,7 @@
         <v>3</v>
       </c>
       <c r="AV229">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW229">
         <v>4</v>
@@ -49529,7 +49532,7 @@
         <v>3</v>
       </c>
       <c r="AV237">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW237">
         <v>4</v>
@@ -50529,7 +50532,7 @@
         <v>4</v>
       </c>
       <c r="AV242">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW242">
         <v>14</v>
@@ -50929,7 +50932,7 @@
         <v>3</v>
       </c>
       <c r="AV244">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW244">
         <v>7</v>
@@ -51729,7 +51732,7 @@
         <v>4</v>
       </c>
       <c r="AV248">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW248">
         <v>11</v>
@@ -53329,7 +53332,7 @@
         <v>3</v>
       </c>
       <c r="AV256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW256">
         <v>9</v>
@@ -54326,7 +54329,7 @@
         <v>1</v>
       </c>
       <c r="AV261">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW261">
         <v>12</v>
@@ -54526,7 +54529,7 @@
         <v>3</v>
       </c>
       <c r="AV262">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW262">
         <v>13</v>
@@ -55526,7 +55529,7 @@
         <v>3</v>
       </c>
       <c r="AV267">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW267">
         <v>7</v>
@@ -56126,7 +56129,7 @@
         <v>3</v>
       </c>
       <c r="AV270">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW270">
         <v>13</v>
@@ -58323,7 +58326,7 @@
         <v>2</v>
       </c>
       <c r="AV281">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW281">
         <v>13</v>
@@ -58523,7 +58526,7 @@
         <v>3</v>
       </c>
       <c r="AV282">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW282">
         <v>1</v>
@@ -59723,7 +59726,7 @@
         <v>1</v>
       </c>
       <c r="AV288">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW288">
         <v>12</v>
@@ -60723,7 +60726,7 @@
         <v>3</v>
       </c>
       <c r="AV293">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW293">
         <v>23</v>
@@ -61723,7 +61726,7 @@
         <v>3</v>
       </c>
       <c r="AV298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW298">
         <v>11</v>
@@ -62323,7 +62326,7 @@
         <v>3</v>
       </c>
       <c r="AV301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW301">
         <v>15</v>
@@ -63123,7 +63126,7 @@
         <v>3</v>
       </c>
       <c r="AV305">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW305">
         <v>6</v>
@@ -63923,7 +63926,7 @@
         <v>2</v>
       </c>
       <c r="AV309">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW309">
         <v>3</v>
@@ -64123,7 +64126,7 @@
         <v>3</v>
       </c>
       <c r="AV310">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW310">
         <v>8</v>
@@ -64523,7 +64526,7 @@
         <v>2</v>
       </c>
       <c r="AV312">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW312">
         <v>6</v>
@@ -67923,7 +67926,7 @@
         <v>2</v>
       </c>
       <c r="AV329">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW329">
         <v>13</v>
@@ -68523,7 +68526,7 @@
         <v>3</v>
       </c>
       <c r="AV332">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW332">
         <v>16</v>
@@ -69123,7 +69126,7 @@
         <v>3</v>
       </c>
       <c r="AV335">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW335">
         <v>6</v>
@@ -70723,7 +70726,7 @@
         <v>3</v>
       </c>
       <c r="AV343">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW343">
         <v>8</v>
@@ -70923,7 +70926,7 @@
         <v>2</v>
       </c>
       <c r="AV344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW344">
         <v>1</v>
@@ -71723,7 +71726,7 @@
         <v>1</v>
       </c>
       <c r="AV348">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW348">
         <v>9</v>
@@ -71923,7 +71926,7 @@
         <v>4</v>
       </c>
       <c r="AV349">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW349">
         <v>12</v>
@@ -73123,7 +73126,7 @@
         <v>5</v>
       </c>
       <c r="AV355">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW355">
         <v>8</v>
@@ -73323,7 +73326,7 @@
         <v>2</v>
       </c>
       <c r="AV356">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW356">
         <v>13</v>
@@ -73523,7 +73526,7 @@
         <v>3</v>
       </c>
       <c r="AV357">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW357">
         <v>8</v>
@@ -73723,7 +73726,7 @@
         <v>2</v>
       </c>
       <c r="AV358">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW358">
         <v>15</v>
@@ -74323,7 +74326,7 @@
         <v>3</v>
       </c>
       <c r="AV361">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW361">
         <v>4</v>
@@ -74923,7 +74926,7 @@
         <v>5</v>
       </c>
       <c r="AV364">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW364">
         <v>1</v>
@@ -75123,7 +75126,7 @@
         <v>4</v>
       </c>
       <c r="AV365">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW365">
         <v>8</v>
@@ -75323,7 +75326,7 @@
         <v>4</v>
       </c>
       <c r="AV366">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW366">
         <v>10</v>
@@ -75923,7 +75926,7 @@
         <v>4</v>
       </c>
       <c r="AV369">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW369">
         <v>10</v>
@@ -76723,7 +76726,7 @@
         <v>3</v>
       </c>
       <c r="AV373">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW373">
         <v>3</v>
@@ -76923,7 +76926,7 @@
         <v>3</v>
       </c>
       <c r="AV374">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW374">
         <v>3</v>
@@ -77123,7 +77126,7 @@
         <v>3</v>
       </c>
       <c r="AV375">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW375">
         <v>12</v>
@@ -78723,7 +78726,7 @@
         <v>4</v>
       </c>
       <c r="AV383">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW383">
         <v>16</v>
@@ -79323,7 +79326,7 @@
         <v>3</v>
       </c>
       <c r="AV386">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW386">
         <v>16</v>
@@ -80123,7 +80126,7 @@
         <v>3</v>
       </c>
       <c r="AV390">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW390">
         <v>11</v>
@@ -80522,6 +80525,9 @@
       <c r="AU392">
         <v>5</v>
       </c>
+      <c r="AV392">
+        <v>1</v>
+      </c>
       <c r="AW392">
         <v>17</v>
       </c>
@@ -81120,7 +81126,7 @@
         <v>3</v>
       </c>
       <c r="AV395">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW395">
         <v>11</v>
@@ -81320,7 +81326,7 @@
         <v>2</v>
       </c>
       <c r="AV396">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW396">
         <v>6</v>
@@ -84117,7 +84123,7 @@
         <v>1</v>
       </c>
       <c r="AV410">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW410">
         <v>17</v>
@@ -86317,7 +86323,7 @@
         <v>1</v>
       </c>
       <c r="AV421">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW421">
         <v>6</v>
@@ -86717,7 +86723,7 @@
         <v>4</v>
       </c>
       <c r="AV423">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW423">
         <v>15</v>
@@ -86917,7 +86923,7 @@
         <v>4</v>
       </c>
       <c r="AV424">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW424">
         <v>5</v>
@@ -87117,7 +87123,7 @@
         <v>3</v>
       </c>
       <c r="AV425">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW425">
         <v>8</v>
@@ -87517,7 +87523,7 @@
         <v>3</v>
       </c>
       <c r="AV427">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW427">
         <v>14</v>
@@ -87917,7 +87923,7 @@
         <v>3</v>
       </c>
       <c r="AV429">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW429">
         <v>1</v>
@@ -88716,6 +88722,9 @@
       <c r="AU433">
         <v>3</v>
       </c>
+      <c r="AV433">
+        <v>2</v>
+      </c>
       <c r="AW433">
         <v>10</v>
       </c>
@@ -90114,7 +90123,7 @@
         <v>5</v>
       </c>
       <c r="AV440">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW440">
         <v>5</v>
@@ -90714,7 +90723,7 @@
         <v>3</v>
       </c>
       <c r="AV443">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW443">
         <v>11</v>
@@ -91314,7 +91323,7 @@
         <v>3</v>
       </c>
       <c r="AV446">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW446">
         <v>6</v>
@@ -91514,7 +91523,7 @@
         <v>3</v>
       </c>
       <c r="AV447">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW447">
         <v>1</v>
@@ -91914,7 +91923,7 @@
         <v>4</v>
       </c>
       <c r="AV449">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW449">
         <v>12</v>
@@ -92514,7 +92523,7 @@
         <v>2</v>
       </c>
       <c r="AV452">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW452">
         <v>7</v>
@@ -92714,7 +92723,7 @@
         <v>3</v>
       </c>
       <c r="AV453">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW453">
         <v>17</v>
@@ -93514,7 +93523,7 @@
         <v>1</v>
       </c>
       <c r="AV457">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW457">
         <v>9</v>
@@ -93914,7 +93923,7 @@
         <v>4</v>
       </c>
       <c r="AV459">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW459">
         <v>13</v>
@@ -94314,7 +94323,7 @@
         <v>3</v>
       </c>
       <c r="AV461">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW461">
         <v>9</v>
